--- a/docs/design-vi/ACSMS-SCR-028/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_増減連絡票（販売店）出力画面_v1.0.xlsx
+++ b/docs/design-vi/ACSMS-SCR-028/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_増減連絡票（販売店）出力画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1363,20 +1363,78 @@
       <c r="AG2" s="10" t="n"/>
       <c r="AH2" s="11" t="n"/>
     </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="18" t="inlineStr"/>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>Đồng bộ với bản tiếng Nhật: tạo カテゴリ6 và bổ sung 7 ca. 041〜044・047 vốn đã có ở bản tiếng Nhật nhưng chưa được dịch (cộng dồn nhiều lịch sử cùng ngày, hủy đăng ký vào giảm bản, đổi cửa hàng bán, người đọc mới không vào phần đổi địa chỉ, phân trang theo đơn vị người đọc). 048＝giới hạn đối tượng tổng hợp chỉ bản giấy (#56408): điều kiện cũ "bản điện tử chỉ tổng hợp khi đã duyệt" đã bị bỏ vì nằm gọn trong giới hạn này. 049＝loại cửa hàng bán dummy khỏi lựa chọn (#56597・`dummy=exclude`), kèm xác nhận cửa hàng đã ngừng kinh doanh cũng không xuất hiện</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="19" t="inlineStr"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="19" t="inlineStr"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="AC2:AH2"/>
     <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="W1:AB1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="W3:AB3"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6239,7 +6297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ56"/>
+  <dimension ref="A1:BQ64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -13812,11 +13870,1550 @@
       <c r="BP56" s="10" t="n"/>
       <c r="BQ56" s="11" t="n"/>
     </row>
+    <row r="57" ht="22.5" customHeight="1">
+      <c r="A57" s="32" t="inlineStr">
+        <is>
+          <t>カテゴリ6: Đối tượng tổng hợp・Lựa chọn cửa hàng bán (Scope / Hanbaiten Options)</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="10" t="n"/>
+      <c r="J57" s="10" t="n"/>
+      <c r="K57" s="10" t="n"/>
+      <c r="L57" s="10" t="n"/>
+      <c r="M57" s="10" t="n"/>
+      <c r="N57" s="10" t="n"/>
+      <c r="O57" s="10" t="n"/>
+      <c r="P57" s="10" t="n"/>
+      <c r="Q57" s="10" t="n"/>
+      <c r="R57" s="10" t="n"/>
+      <c r="S57" s="10" t="n"/>
+      <c r="T57" s="10" t="n"/>
+      <c r="U57" s="10" t="n"/>
+      <c r="V57" s="10" t="n"/>
+      <c r="W57" s="10" t="n"/>
+      <c r="X57" s="10" t="n"/>
+      <c r="Y57" s="10" t="n"/>
+      <c r="Z57" s="10" t="n"/>
+      <c r="AA57" s="10" t="n"/>
+      <c r="AB57" s="10" t="n"/>
+      <c r="AC57" s="10" t="n"/>
+      <c r="AD57" s="10" t="n"/>
+      <c r="AE57" s="10" t="n"/>
+      <c r="AF57" s="10" t="n"/>
+      <c r="AG57" s="10" t="n"/>
+      <c r="AH57" s="10" t="n"/>
+      <c r="AI57" s="10" t="n"/>
+      <c r="AJ57" s="10" t="n"/>
+      <c r="AK57" s="10" t="n"/>
+      <c r="AL57" s="10" t="n"/>
+      <c r="AM57" s="10" t="n"/>
+      <c r="AN57" s="10" t="n"/>
+      <c r="AO57" s="10" t="n"/>
+      <c r="AP57" s="10" t="n"/>
+      <c r="AQ57" s="10" t="n"/>
+      <c r="AR57" s="10" t="n"/>
+      <c r="AS57" s="10" t="n"/>
+      <c r="AT57" s="10" t="n"/>
+      <c r="AU57" s="10" t="n"/>
+      <c r="AV57" s="10" t="n"/>
+      <c r="AW57" s="10" t="n"/>
+      <c r="AX57" s="10" t="n"/>
+      <c r="AY57" s="10" t="n"/>
+      <c r="AZ57" s="10" t="n"/>
+      <c r="BA57" s="10" t="n"/>
+      <c r="BB57" s="10" t="n"/>
+      <c r="BC57" s="10" t="n"/>
+      <c r="BD57" s="10" t="n"/>
+      <c r="BE57" s="10" t="n"/>
+      <c r="BF57" s="10" t="n"/>
+      <c r="BG57" s="10" t="n"/>
+      <c r="BH57" s="10" t="n"/>
+      <c r="BI57" s="10" t="n"/>
+      <c r="BJ57" s="10" t="n"/>
+      <c r="BK57" s="10" t="n"/>
+      <c r="BL57" s="10" t="n"/>
+      <c r="BM57" s="10" t="n"/>
+      <c r="BN57" s="10" t="n"/>
+      <c r="BO57" s="10" t="n"/>
+      <c r="BP57" s="10" t="n"/>
+      <c r="BQ57" s="11" t="n"/>
+    </row>
+    <row r="58" ht="192" customHeight="1">
+      <c r="A58" s="44" t="n">
+        <v>41</v>
+      </c>
+      <c r="B58" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-028-041</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="11" t="n"/>
+      <c r="E58" s="46" t="inlineStr">
+        <is>
+          <t>Cộng dồn nhiều lịch sử trong cùng ngày (1→3→5 thành 1→5)</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="10" t="n"/>
+      <c r="I58" s="11" t="n"/>
+      <c r="J58" s="46" t="inlineStr">
+        <is>
+          <t>・Đã đăng nhập bằng CHUOKAI
+・Tồn tại lịch sử cùng một người đọc đổi số bản nhiều lần trong cùng ngày áp dụng theo 1→3→5 (từ 2 bản ghi trở lên trong cùng ngày)</t>
+        </is>
+      </c>
+      <c r="K58" s="10" t="n"/>
+      <c r="L58" s="10" t="n"/>
+      <c r="M58" s="10" t="n"/>
+      <c r="N58" s="10" t="n"/>
+      <c r="O58" s="10" t="n"/>
+      <c r="P58" s="11" t="n"/>
+      <c r="Q58" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Nhập ngày áp dụng đó rồi thực thi「レポートプレビュー」
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Kiểm tra người đọc tương ứng trong bảng tăng bản</t>
+          </r>
+        </is>
+      </c>
+      <c r="R58" s="10" t="n"/>
+      <c r="S58" s="10" t="n"/>
+      <c r="T58" s="10" t="n"/>
+      <c r="U58" s="10" t="n"/>
+      <c r="V58" s="10" t="n"/>
+      <c r="W58" s="11" t="n"/>
+      <c r="X58" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Danh sách được hiển thị
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Người đọc tương ứng hiển thị bằng **1 dòng chứ không phải 2 dòng** (cộng dồn trong ngày)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Số bản hiển thị là **「1 → 5」** (số bản trước đó lúc đầu ngày → số bản hiện tại lúc cuối ngày)</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y58" s="10" t="n"/>
+      <c r="Z58" s="10" t="n"/>
+      <c r="AA58" s="10" t="n"/>
+      <c r="AB58" s="10" t="n"/>
+      <c r="AC58" s="10" t="n"/>
+      <c r="AD58" s="11" t="n"/>
+      <c r="AE58" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF58" s="11" t="n"/>
+      <c r="AG58" s="45" t="inlineStr"/>
+      <c r="AH58" s="10" t="n"/>
+      <c r="AI58" s="11" t="n"/>
+      <c r="AJ58" s="45" t="inlineStr"/>
+      <c r="AK58" s="10" t="n"/>
+      <c r="AL58" s="11" t="n"/>
+      <c r="AM58" s="45" t="inlineStr"/>
+      <c r="AN58" s="10" t="n"/>
+      <c r="AO58" s="11" t="n"/>
+      <c r="AP58" s="45" t="inlineStr"/>
+      <c r="AQ58" s="10" t="n"/>
+      <c r="AR58" s="11" t="n"/>
+      <c r="AS58" s="45" t="inlineStr"/>
+      <c r="AT58" s="10" t="n"/>
+      <c r="AU58" s="11" t="n"/>
+      <c r="AV58" s="45" t="inlineStr"/>
+      <c r="AW58" s="10" t="n"/>
+      <c r="AX58" s="11" t="n"/>
+      <c r="AY58" s="45" t="inlineStr"/>
+      <c r="AZ58" s="10" t="n"/>
+      <c r="BA58" s="11" t="n"/>
+      <c r="BB58" s="45" t="inlineStr"/>
+      <c r="BC58" s="10" t="n"/>
+      <c r="BD58" s="11" t="n"/>
+      <c r="BE58" s="45" t="inlineStr"/>
+      <c r="BF58" s="10" t="n"/>
+      <c r="BG58" s="11" t="n"/>
+      <c r="BH58" s="45" t="inlineStr"/>
+      <c r="BI58" s="10" t="n"/>
+      <c r="BJ58" s="11" t="n"/>
+      <c r="BK58" s="46" t="inlineStr">
+        <is>
+          <t>(không có)</t>
+        </is>
+      </c>
+      <c r="BL58" s="10" t="n"/>
+      <c r="BM58" s="10" t="n"/>
+      <c r="BN58" s="10" t="n"/>
+      <c r="BO58" s="10" t="n"/>
+      <c r="BP58" s="10" t="n"/>
+      <c r="BQ58" s="11" t="n"/>
+    </row>
+    <row r="59" ht="128" customHeight="1">
+      <c r="A59" s="44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B59" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-028-042</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="11" t="n"/>
+      <c r="E59" s="46" t="inlineStr">
+        <is>
+          <t>Hủy đăng ký (…→0) được phản ánh vào giảm bản</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="n"/>
+      <c r="G59" s="10" t="n"/>
+      <c r="H59" s="10" t="n"/>
+      <c r="I59" s="11" t="n"/>
+      <c r="J59" s="46" t="inlineStr">
+        <is>
+          <t>・Đã đăng nhập bằng CHUOKAI
+・Tồn tại người đọc đã hủy đăng ký (số bản đọc 2→0) vào ngày áp dụng đó</t>
+        </is>
+      </c>
+      <c r="K59" s="10" t="n"/>
+      <c r="L59" s="10" t="n"/>
+      <c r="M59" s="10" t="n"/>
+      <c r="N59" s="10" t="n"/>
+      <c r="O59" s="10" t="n"/>
+      <c r="P59" s="11" t="n"/>
+      <c r="Q59" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Nhập ngày áp dụng đó rồi thực thi「レポートプレビュー」
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Kiểm tra nội dung của bảng giảm bản</t>
+          </r>
+        </is>
+      </c>
+      <c r="R59" s="10" t="n"/>
+      <c r="S59" s="10" t="n"/>
+      <c r="T59" s="10" t="n"/>
+      <c r="U59" s="10" t="n"/>
+      <c r="V59" s="10" t="n"/>
+      <c r="W59" s="11" t="n"/>
+      <c r="X59" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Danh sách được hiển thị
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Người đọc đã hủy đăng ký hiển thị trong bảng giảm bản
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Số bản hiển thị là **「2 → 0」**</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y59" s="10" t="n"/>
+      <c r="Z59" s="10" t="n"/>
+      <c r="AA59" s="10" t="n"/>
+      <c r="AB59" s="10" t="n"/>
+      <c r="AC59" s="10" t="n"/>
+      <c r="AD59" s="11" t="n"/>
+      <c r="AE59" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF59" s="11" t="n"/>
+      <c r="AG59" s="45" t="inlineStr"/>
+      <c r="AH59" s="10" t="n"/>
+      <c r="AI59" s="11" t="n"/>
+      <c r="AJ59" s="45" t="inlineStr"/>
+      <c r="AK59" s="10" t="n"/>
+      <c r="AL59" s="11" t="n"/>
+      <c r="AM59" s="45" t="inlineStr"/>
+      <c r="AN59" s="10" t="n"/>
+      <c r="AO59" s="11" t="n"/>
+      <c r="AP59" s="45" t="inlineStr"/>
+      <c r="AQ59" s="10" t="n"/>
+      <c r="AR59" s="11" t="n"/>
+      <c r="AS59" s="45" t="inlineStr"/>
+      <c r="AT59" s="10" t="n"/>
+      <c r="AU59" s="11" t="n"/>
+      <c r="AV59" s="45" t="inlineStr"/>
+      <c r="AW59" s="10" t="n"/>
+      <c r="AX59" s="11" t="n"/>
+      <c r="AY59" s="45" t="inlineStr"/>
+      <c r="AZ59" s="10" t="n"/>
+      <c r="BA59" s="11" t="n"/>
+      <c r="BB59" s="45" t="inlineStr"/>
+      <c r="BC59" s="10" t="n"/>
+      <c r="BD59" s="11" t="n"/>
+      <c r="BE59" s="45" t="inlineStr"/>
+      <c r="BF59" s="10" t="n"/>
+      <c r="BG59" s="11" t="n"/>
+      <c r="BH59" s="45" t="inlineStr"/>
+      <c r="BI59" s="10" t="n"/>
+      <c r="BJ59" s="11" t="n"/>
+      <c r="BK59" s="46" t="inlineStr">
+        <is>
+          <t>(không có)</t>
+        </is>
+      </c>
+      <c r="BL59" s="10" t="n"/>
+      <c r="BM59" s="10" t="n"/>
+      <c r="BN59" s="10" t="n"/>
+      <c r="BO59" s="10" t="n"/>
+      <c r="BP59" s="10" t="n"/>
+      <c r="BQ59" s="11" t="n"/>
+    </row>
+    <row r="60" ht="192" customHeight="1">
+      <c r="A60" s="44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B60" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-028-043</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="11" t="n"/>
+      <c r="E60" s="46" t="inlineStr">
+        <is>
+          <t>Đổi cửa hàng bán (giảm ở cửa hàng cũ / tăng ở cửa hàng mới)</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="11" t="n"/>
+      <c r="J60" s="46" t="inlineStr">
+        <is>
+          <t>・Đã đăng nhập bằng CHUOKAI
+・Tồn tại người đọc đã đổi cửa hàng bán từ A→B vào ngày áp dụng đó (số bản không đổi 1→1)</t>
+        </is>
+      </c>
+      <c r="K60" s="10" t="n"/>
+      <c r="L60" s="10" t="n"/>
+      <c r="M60" s="10" t="n"/>
+      <c r="N60" s="10" t="n"/>
+      <c r="O60" s="10" t="n"/>
+      <c r="P60" s="11" t="n"/>
+      <c r="Q60" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Nhập ngày áp dụng đó rồi thực thi「レポートプレビュー」
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Kiểm tra báo biểu của cửa hàng cũ A và cửa hàng mới B</t>
+          </r>
+        </is>
+      </c>
+      <c r="R60" s="10" t="n"/>
+      <c r="S60" s="10" t="n"/>
+      <c r="T60" s="10" t="n"/>
+      <c r="U60" s="10" t="n"/>
+      <c r="V60" s="10" t="n"/>
+      <c r="W60" s="11" t="n"/>
+      <c r="X60" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Danh sách được hiển thị
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Người đọc tương ứng hiển thị ở phần **giảm bản** của cửa hàng cũ A (số bản「1 → 0」)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Người đọc tương ứng hiển thị ở phần **tăng bản** của cửa hàng mới B (số bản「0 → 1」)</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y60" s="10" t="n"/>
+      <c r="Z60" s="10" t="n"/>
+      <c r="AA60" s="10" t="n"/>
+      <c r="AB60" s="10" t="n"/>
+      <c r="AC60" s="10" t="n"/>
+      <c r="AD60" s="11" t="n"/>
+      <c r="AE60" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF60" s="11" t="n"/>
+      <c r="AG60" s="45" t="inlineStr"/>
+      <c r="AH60" s="10" t="n"/>
+      <c r="AI60" s="11" t="n"/>
+      <c r="AJ60" s="45" t="inlineStr"/>
+      <c r="AK60" s="10" t="n"/>
+      <c r="AL60" s="11" t="n"/>
+      <c r="AM60" s="45" t="inlineStr"/>
+      <c r="AN60" s="10" t="n"/>
+      <c r="AO60" s="11" t="n"/>
+      <c r="AP60" s="45" t="inlineStr"/>
+      <c r="AQ60" s="10" t="n"/>
+      <c r="AR60" s="11" t="n"/>
+      <c r="AS60" s="45" t="inlineStr"/>
+      <c r="AT60" s="10" t="n"/>
+      <c r="AU60" s="11" t="n"/>
+      <c r="AV60" s="45" t="inlineStr"/>
+      <c r="AW60" s="10" t="n"/>
+      <c r="AX60" s="11" t="n"/>
+      <c r="AY60" s="45" t="inlineStr"/>
+      <c r="AZ60" s="10" t="n"/>
+      <c r="BA60" s="11" t="n"/>
+      <c r="BB60" s="45" t="inlineStr"/>
+      <c r="BC60" s="10" t="n"/>
+      <c r="BD60" s="11" t="n"/>
+      <c r="BE60" s="45" t="inlineStr"/>
+      <c r="BF60" s="10" t="n"/>
+      <c r="BG60" s="11" t="n"/>
+      <c r="BH60" s="45" t="inlineStr"/>
+      <c r="BI60" s="10" t="n"/>
+      <c r="BJ60" s="11" t="n"/>
+      <c r="BK60" s="46" t="inlineStr">
+        <is>
+          <t>Do chi nhánh quản lý của cửa hàng bán cũ không được lưu trong lịch sử, tạm thời dùng chi nhánh quản lý của bản ghi cuối cùng trong ngày.</t>
+        </is>
+      </c>
+      <c r="BL60" s="10" t="n"/>
+      <c r="BM60" s="10" t="n"/>
+      <c r="BN60" s="10" t="n"/>
+      <c r="BO60" s="10" t="n"/>
+      <c r="BP60" s="10" t="n"/>
+      <c r="BQ60" s="11" t="n"/>
+    </row>
+    <row r="61" ht="160" customHeight="1">
+      <c r="A61" s="44" t="n">
+        <v>44</v>
+      </c>
+      <c r="B61" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-028-044</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="11" t="n"/>
+      <c r="E61" s="46" t="inlineStr">
+        <is>
+          <t>Người đọc mới không đưa vào phần thay đổi địa chỉ</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="10" t="n"/>
+      <c r="I61" s="11" t="n"/>
+      <c r="J61" s="46" t="inlineStr">
+        <is>
+          <t>・Đã đăng nhập bằng CHUOKAI
+・Tồn tại người đọc bắt đầu đăng ký mới vào ngày áp dụng đó (lịch sử đầu tiên・địa chỉ lần trước trống)</t>
+        </is>
+      </c>
+      <c r="K61" s="10" t="n"/>
+      <c r="L61" s="10" t="n"/>
+      <c r="M61" s="10" t="n"/>
+      <c r="N61" s="10" t="n"/>
+      <c r="O61" s="10" t="n"/>
+      <c r="P61" s="11" t="n"/>
+      <c r="Q61" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Nhập ngày áp dụng đó rồi thực thi「レポートプレビュー」
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Kiểm tra bảng tăng bản và bảng thay đổi địa chỉ</t>
+          </r>
+        </is>
+      </c>
+      <c r="R61" s="10" t="n"/>
+      <c r="S61" s="10" t="n"/>
+      <c r="T61" s="10" t="n"/>
+      <c r="U61" s="10" t="n"/>
+      <c r="V61" s="10" t="n"/>
+      <c r="W61" s="11" t="n"/>
+      <c r="X61" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Danh sách được hiển thị
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Người đọc mới hiển thị ở phần **tăng bản** (「0 → 1」)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Người đọc mới **không hiển thị trong bảng thay đổi địa chỉ** (vì địa chỉ lần trước trống)</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y61" s="10" t="n"/>
+      <c r="Z61" s="10" t="n"/>
+      <c r="AA61" s="10" t="n"/>
+      <c r="AB61" s="10" t="n"/>
+      <c r="AC61" s="10" t="n"/>
+      <c r="AD61" s="11" t="n"/>
+      <c r="AE61" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF61" s="11" t="n"/>
+      <c r="AG61" s="45" t="inlineStr"/>
+      <c r="AH61" s="10" t="n"/>
+      <c r="AI61" s="11" t="n"/>
+      <c r="AJ61" s="45" t="inlineStr"/>
+      <c r="AK61" s="10" t="n"/>
+      <c r="AL61" s="11" t="n"/>
+      <c r="AM61" s="45" t="inlineStr"/>
+      <c r="AN61" s="10" t="n"/>
+      <c r="AO61" s="11" t="n"/>
+      <c r="AP61" s="45" t="inlineStr"/>
+      <c r="AQ61" s="10" t="n"/>
+      <c r="AR61" s="11" t="n"/>
+      <c r="AS61" s="45" t="inlineStr"/>
+      <c r="AT61" s="10" t="n"/>
+      <c r="AU61" s="11" t="n"/>
+      <c r="AV61" s="45" t="inlineStr"/>
+      <c r="AW61" s="10" t="n"/>
+      <c r="AX61" s="11" t="n"/>
+      <c r="AY61" s="45" t="inlineStr"/>
+      <c r="AZ61" s="10" t="n"/>
+      <c r="BA61" s="11" t="n"/>
+      <c r="BB61" s="45" t="inlineStr"/>
+      <c r="BC61" s="10" t="n"/>
+      <c r="BD61" s="11" t="n"/>
+      <c r="BE61" s="45" t="inlineStr"/>
+      <c r="BF61" s="10" t="n"/>
+      <c r="BG61" s="11" t="n"/>
+      <c r="BH61" s="45" t="inlineStr"/>
+      <c r="BI61" s="10" t="n"/>
+      <c r="BJ61" s="11" t="n"/>
+      <c r="BK61" s="46" t="inlineStr">
+        <is>
+          <t>(không có)</t>
+        </is>
+      </c>
+      <c r="BL61" s="10" t="n"/>
+      <c r="BM61" s="10" t="n"/>
+      <c r="BN61" s="10" t="n"/>
+      <c r="BO61" s="10" t="n"/>
+      <c r="BP61" s="10" t="n"/>
+      <c r="BQ61" s="11" t="n"/>
+    </row>
+    <row r="62" ht="432" customHeight="1">
+      <c r="A62" s="44" t="n">
+        <v>45</v>
+      </c>
+      <c r="B62" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-028-047</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="11" t="n"/>
+      <c r="E62" s="46" t="inlineStr">
+        <is>
+          <t>Phân trang (SQL OFFSET/LIMIT・theo đơn vị người đọc・API riêng)</t>
+        </is>
+      </c>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
+      <c r="H62" s="10" t="n"/>
+      <c r="I62" s="11" t="n"/>
+      <c r="J62" s="46" t="inlineStr">
+        <is>
+          <t>・Đã đăng nhập bằng CHUOKAI
+・Tồn tại từ 16 người đọc thuộc đối tượng tăng giảm trở lên vào ngày áp dụng đó</t>
+        </is>
+      </c>
+      <c r="K62" s="10" t="n"/>
+      <c r="L62" s="10" t="n"/>
+      <c r="M62" s="10" t="n"/>
+      <c r="N62" s="10" t="n"/>
+      <c r="O62" s="10" t="n"/>
+      <c r="P62" s="11" t="n"/>
+      <c r="Q62" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Nhập ngày áp dụng rồi thực thi「レポートプレビュー」
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Chuyển sang trang 2 bằng pager ở dưới phần preview</t>
+          </r>
+        </is>
+      </c>
+      <c r="R62" s="10" t="n"/>
+      <c r="S62" s="10" t="n"/>
+      <c r="T62" s="10" t="n"/>
+      <c r="U62" s="10" t="n"/>
+      <c r="V62" s="10" t="n"/>
+      <c r="W62" s="11" t="n"/>
+      <c r="X62" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Trang 1 hiển thị tối đa **15 người đọc** (≒15 bản ghi. Phần lớn là 1 bản ghi/người đọc. Do đổi cửa hàng bán＝2 / đổi số bản＋địa chỉ＝2 nên không chính xác đúng 15 dòng)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Pager (tổng N bản ghi ＝ số người đọc thuộc đối tượng・trang 1/M) được hiển thị
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・「ページ数」ở header báo biểu là `1/M`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・BE chỉ load chi tiết của số người đọc trong 1 trang bằng `COUNT(DISTINCT dokusya_id)` ＋ OFFSET/LIMIT trên `dokusya_id` (không load toàn bộ)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Lấy lại trang 2 bằng API riêng và hiển thị những người đọc còn lại (trình duyệt chỉ vẽ 1 trang)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・「ページ数」được cập nhật thành `2/M`</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y62" s="10" t="n"/>
+      <c r="Z62" s="10" t="n"/>
+      <c r="AA62" s="10" t="n"/>
+      <c r="AB62" s="10" t="n"/>
+      <c r="AC62" s="10" t="n"/>
+      <c r="AD62" s="11" t="n"/>
+      <c r="AE62" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF62" s="11" t="n"/>
+      <c r="AG62" s="45" t="inlineStr"/>
+      <c r="AH62" s="10" t="n"/>
+      <c r="AI62" s="11" t="n"/>
+      <c r="AJ62" s="45" t="inlineStr"/>
+      <c r="AK62" s="10" t="n"/>
+      <c r="AL62" s="11" t="n"/>
+      <c r="AM62" s="45" t="inlineStr"/>
+      <c r="AN62" s="10" t="n"/>
+      <c r="AO62" s="11" t="n"/>
+      <c r="AP62" s="45" t="inlineStr"/>
+      <c r="AQ62" s="10" t="n"/>
+      <c r="AR62" s="11" t="n"/>
+      <c r="AS62" s="45" t="inlineStr"/>
+      <c r="AT62" s="10" t="n"/>
+      <c r="AU62" s="11" t="n"/>
+      <c r="AV62" s="45" t="inlineStr"/>
+      <c r="AW62" s="10" t="n"/>
+      <c r="AX62" s="11" t="n"/>
+      <c r="AY62" s="45" t="inlineStr"/>
+      <c r="AZ62" s="10" t="n"/>
+      <c r="BA62" s="11" t="n"/>
+      <c r="BB62" s="45" t="inlineStr"/>
+      <c r="BC62" s="10" t="n"/>
+      <c r="BD62" s="11" t="n"/>
+      <c r="BE62" s="45" t="inlineStr"/>
+      <c r="BF62" s="10" t="n"/>
+      <c r="BG62" s="11" t="n"/>
+      <c r="BH62" s="45" t="inlineStr"/>
+      <c r="BI62" s="10" t="n"/>
+      <c r="BJ62" s="11" t="n"/>
+      <c r="BK62" s="46" t="inlineStr">
+        <is>
+          <t>Việc xuất báo biểu điện tử (PDF) không phân trang mà xuất toàn bộ vào 1 file PDF.</t>
+        </is>
+      </c>
+      <c r="BL62" s="10" t="n"/>
+      <c r="BM62" s="10" t="n"/>
+      <c r="BN62" s="10" t="n"/>
+      <c r="BO62" s="10" t="n"/>
+      <c r="BP62" s="10" t="n"/>
+      <c r="BQ62" s="11" t="n"/>
+    </row>
+    <row r="63" ht="450" customHeight="1">
+      <c r="A63" s="44" t="n">
+        <v>46</v>
+      </c>
+      <c r="B63" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-028-048</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="11" t="n"/>
+      <c r="E63" s="46" t="inlineStr">
+        <is>
+          <t>Giới hạn đối tượng tổng hợp chỉ bản giấy (#56408)</t>
+        </is>
+      </c>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
+      <c r="I63" s="11" t="n"/>
+      <c r="J63" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN (có quyền `report.export_zougen_hanbaiten`)
+・Lấy ngày áp dụng là 2026/09/01, chuẩn bị người đọc có lịch sử thuộc đối tượng báo cáo tăng giảm (`zougen_hokoku_flg = true`) trong cùng ngày như sau (tất cả đều thuộc cửa hàng bán A có thật)
+・(a) Bản giấy (dokusya_shubetsu=1) tăng từ 1 → 3 bản, 1 người
+・(b) Kết hợp (3) có thay đổi số bản, 1 người
+・(c) Bản điện tử (2)・đã duyệt (denshi_shonin_status=1) 1 người
+・(d) Bản điện tử (2)・chưa duyệt 1 người</t>
+        </is>
+      </c>
+      <c r="K63" s="10" t="n"/>
+      <c r="L63" s="10" t="n"/>
+      <c r="M63" s="10" t="n"/>
+      <c r="N63" s="10" t="n"/>
+      <c r="O63" s="10" t="n"/>
+      <c r="P63" s="11" t="n"/>
+      <c r="Q63" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Hiển thị preview với ngày áp dụng 2026/09/01 và kiểm tra người đọc thuộc đối tượng
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Xuất PDF và kiểm tra số bản tăng・số bản giảm của cửa hàng bán A
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Kiểm tra người đọc (b) kết hợp có nằm trong bản xuất không
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Kiểm tra người đọc (c) bản điện tử・đã duyệt có nằm trong bản xuất không
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Xuất ở trạng thái chỉ giữ lại (a) và xóa các trường hợp còn lại, xác nhận số lượng khớp</t>
+          </r>
+        </is>
+      </c>
+      <c r="R63" s="10" t="n"/>
+      <c r="S63" s="10" t="n"/>
+      <c r="T63" s="10" t="n"/>
+      <c r="U63" s="10" t="n"/>
+      <c r="V63" s="10" t="n"/>
+      <c r="W63" s="11" t="n"/>
+      <c r="X63" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">**Chỉ (a) bản giấy 1 người** thuộc đối tượng
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Số bản tăng của cửa hàng bán A chỉ gồm phần tăng của (a) (+2 bản)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">**Không nằm trong bản xuất**. Kết hợp không có biến động tương ứng với mục đích của báo biểu này là "truyền đạt tăng giảm số bản giao báo tới cửa hàng bán"
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">**Không nằm trong bản xuất**. Trước đây có điều kiện "bản điện tử chỉ tổng hợp khi đã duyệt", nhưng điều kiện đó đã bị bỏ vì nằm gọn trong giới hạn chỉ bản giấy (yêu cầu khách hàng 2026-08 / #56408)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Nội dung xuất ra không thay đổi
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Báo biểu này truyền đạt tăng giảm số bản giao báo tới cửa hàng bán, mà bản điện tử・kết hợp không có khái niệm giao báo (bản điện tử đơn thuần thì gắn với cửa hàng dummy)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Thông báo tăng giảm (SCR-029) cũng giới hạn chỉ bản giấy, nhưng điều kiện do từng màn tự giữ (không dùng chung nên nếu chỉ sửa một bên sẽ lệch nhau)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Danh sách người đọc (SCR-026) có đối tượng khác nhau theo loại báo biểu (theo chi nhánh quản lý thì kết hợp・bản điện tử cũng thuộc đối tượng). Không được dùng lại nguyên điều kiện của màn hình này</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y63" s="10" t="n"/>
+      <c r="Z63" s="10" t="n"/>
+      <c r="AA63" s="10" t="n"/>
+      <c r="AB63" s="10" t="n"/>
+      <c r="AC63" s="10" t="n"/>
+      <c r="AD63" s="11" t="n"/>
+      <c r="AE63" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF63" s="11" t="n"/>
+      <c r="AG63" s="45" t="inlineStr"/>
+      <c r="AH63" s="10" t="n"/>
+      <c r="AI63" s="11" t="n"/>
+      <c r="AJ63" s="45" t="inlineStr"/>
+      <c r="AK63" s="10" t="n"/>
+      <c r="AL63" s="11" t="n"/>
+      <c r="AM63" s="45" t="inlineStr"/>
+      <c r="AN63" s="10" t="n"/>
+      <c r="AO63" s="11" t="n"/>
+      <c r="AP63" s="45" t="inlineStr"/>
+      <c r="AQ63" s="10" t="n"/>
+      <c r="AR63" s="11" t="n"/>
+      <c r="AS63" s="45" t="inlineStr"/>
+      <c r="AT63" s="10" t="n"/>
+      <c r="AU63" s="11" t="n"/>
+      <c r="AV63" s="45" t="inlineStr"/>
+      <c r="AW63" s="10" t="n"/>
+      <c r="AX63" s="11" t="n"/>
+      <c r="AY63" s="45" t="inlineStr"/>
+      <c r="AZ63" s="10" t="n"/>
+      <c r="BA63" s="11" t="n"/>
+      <c r="BB63" s="45" t="inlineStr"/>
+      <c r="BC63" s="10" t="n"/>
+      <c r="BD63" s="11" t="n"/>
+      <c r="BE63" s="45" t="inlineStr"/>
+      <c r="BF63" s="10" t="n"/>
+      <c r="BG63" s="11" t="n"/>
+      <c r="BH63" s="45" t="inlineStr"/>
+      <c r="BI63" s="10" t="n"/>
+      <c r="BJ63" s="11" t="n"/>
+      <c r="BK63" s="46" t="inlineStr">
+        <is>
+          <t>(không có)</t>
+        </is>
+      </c>
+      <c r="BL63" s="10" t="n"/>
+      <c r="BM63" s="10" t="n"/>
+      <c r="BN63" s="10" t="n"/>
+      <c r="BO63" s="10" t="n"/>
+      <c r="BP63" s="10" t="n"/>
+      <c r="BQ63" s="11" t="n"/>
+    </row>
+    <row r="64" ht="450" customHeight="1">
+      <c r="A64" s="44" t="n">
+        <v>47</v>
+      </c>
+      <c r="B64" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-028-049</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="11" t="n"/>
+      <c r="E64" s="46" t="inlineStr">
+        <is>
+          <t>Loại cửa hàng bán dummy của bản điện tử khỏi lựa chọn (#56597)</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
+      <c r="H64" s="10" t="n"/>
+      <c r="I64" s="11" t="n"/>
+      <c r="J64" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN (có quyền `report.export_zougen_hanbaiten`)
+・JA của mình có cửa hàng bán dummy của bản điện tử (`hanbaiten_code = 9999999999`) và có người đọc bản điện tử gắn vào
+・Tồn tại từ 2 cửa hàng bán có thật trở lên
+・Chuẩn bị thêm 1 cửa hàng bán có cờ ngừng kinh doanh (`haiten_flg = true`)</t>
+        </is>
+      </c>
+      <c r="K64" s="10" t="n"/>
+      <c r="L64" s="10" t="n"/>
+      <c r="M64" s="10" t="n"/>
+      <c r="N64" s="10" t="n"/>
+      <c r="O64" s="10" t="n"/>
+      <c r="P64" s="11" t="n"/>
+      <c r="Q64" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Mở dropdown「販売店」trong điều kiện xuất và kiểm tra các lựa chọn
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Kiểm tra tham số request của `GET /api/v1/hanbaiten/dropdown`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Kiểm tra cửa hàng bán đã ngừng kinh doanh có xuất hiện trong lựa chọn không
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Từ DevTools chỉ định trực tiếp `hanbaiten_id` của cửa hàng dummy và gọi API xuất</t>
+          </r>
+        </is>
+      </c>
+      <c r="R64" s="10" t="n"/>
+      <c r="S64" s="10" t="n"/>
+      <c r="T64" s="10" t="n"/>
+      <c r="U64" s="10" t="n"/>
+      <c r="V64" s="10" t="n"/>
+      <c r="W64" s="11" t="n"/>
+      <c r="X64" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Chỉ các cửa hàng bán có thật và chưa ngừng kinh doanh hiển thị trong lựa chọn, **cửa hàng dummy (9999999999) không xuất hiện**
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Có chỉ định `dummy=exclude`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Cửa hàng bán đã ngừng kinh doanh cũng không xuất hiện trong lựa chọn (phía SQL tổng hợp cũng loại bằng `h.haiten_flg = false`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Kết quả là 0 bản ghi. Đối tượng tổng hợp của báo biểu này chỉ là bản giấy, mà gắn với dummy chỉ có người đọc bản điện tử, nên dù chọn được cũng chắc chắn ra 0
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Cửa hàng bán dummy của bản điện tử là "nơi hứng để gắn người đọc bản điện tử", không phải cửa hàng bán có thật (tồn tại vì `t_dokusya.hanbaiten_id` là NOT NULL)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Việc loại trừ tương tự cũng áp dụng cho danh sách người đọc theo cửa hàng bán (SCR-026) (xem ACSMS-TC-026-044)</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y64" s="10" t="n"/>
+      <c r="Z64" s="10" t="n"/>
+      <c r="AA64" s="10" t="n"/>
+      <c r="AB64" s="10" t="n"/>
+      <c r="AC64" s="10" t="n"/>
+      <c r="AD64" s="11" t="n"/>
+      <c r="AE64" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF64" s="11" t="n"/>
+      <c r="AG64" s="45" t="inlineStr"/>
+      <c r="AH64" s="10" t="n"/>
+      <c r="AI64" s="11" t="n"/>
+      <c r="AJ64" s="45" t="inlineStr"/>
+      <c r="AK64" s="10" t="n"/>
+      <c r="AL64" s="11" t="n"/>
+      <c r="AM64" s="45" t="inlineStr"/>
+      <c r="AN64" s="10" t="n"/>
+      <c r="AO64" s="11" t="n"/>
+      <c r="AP64" s="45" t="inlineStr"/>
+      <c r="AQ64" s="10" t="n"/>
+      <c r="AR64" s="11" t="n"/>
+      <c r="AS64" s="45" t="inlineStr"/>
+      <c r="AT64" s="10" t="n"/>
+      <c r="AU64" s="11" t="n"/>
+      <c r="AV64" s="45" t="inlineStr"/>
+      <c r="AW64" s="10" t="n"/>
+      <c r="AX64" s="11" t="n"/>
+      <c r="AY64" s="45" t="inlineStr"/>
+      <c r="AZ64" s="10" t="n"/>
+      <c r="BA64" s="11" t="n"/>
+      <c r="BB64" s="45" t="inlineStr"/>
+      <c r="BC64" s="10" t="n"/>
+      <c r="BD64" s="11" t="n"/>
+      <c r="BE64" s="45" t="inlineStr"/>
+      <c r="BF64" s="10" t="n"/>
+      <c r="BG64" s="11" t="n"/>
+      <c r="BH64" s="45" t="inlineStr"/>
+      <c r="BI64" s="10" t="n"/>
+      <c r="BJ64" s="11" t="n"/>
+      <c r="BK64" s="46" t="inlineStr">
+        <is>
+          <t>(không có)
+---</t>
+        </is>
+      </c>
+      <c r="BL64" s="10" t="n"/>
+      <c r="BM64" s="10" t="n"/>
+      <c r="BN64" s="10" t="n"/>
+      <c r="BO64" s="10" t="n"/>
+      <c r="BP64" s="10" t="n"/>
+      <c r="BQ64" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="751">
+  <mergeCells count="871">
+    <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
+    <mergeCell ref="B60:D60"/>
     <mergeCell ref="Q27:W27"/>
     <mergeCell ref="AS46:AU46"/>
+    <mergeCell ref="BK58:BQ58"/>
     <mergeCell ref="AP50:AR50"/>
     <mergeCell ref="AE54:AF54"/>
     <mergeCell ref="BH33:BJ33"/>
@@ -13824,15 +15421,20 @@
     <mergeCell ref="AE41:AF41"/>
     <mergeCell ref="E52:I52"/>
     <mergeCell ref="B53:D53"/>
+    <mergeCell ref="AP60:AR60"/>
     <mergeCell ref="E39:I39"/>
     <mergeCell ref="E14:I14"/>
+    <mergeCell ref="AS61:AU61"/>
     <mergeCell ref="W7:Y7"/>
+    <mergeCell ref="AM64:AO64"/>
     <mergeCell ref="AS48:AU48"/>
+    <mergeCell ref="J62:P62"/>
     <mergeCell ref="BK16:BQ16"/>
     <mergeCell ref="AE56:AF56"/>
     <mergeCell ref="AE43:AF43"/>
     <mergeCell ref="AM30:AO30"/>
     <mergeCell ref="AP45:AR45"/>
+    <mergeCell ref="J64:P64"/>
     <mergeCell ref="BE13:BG13"/>
     <mergeCell ref="W8:Y8"/>
     <mergeCell ref="Q37:W37"/>
@@ -13855,6 +15457,7 @@
     <mergeCell ref="AS51:AU51"/>
     <mergeCell ref="Q15:W15"/>
     <mergeCell ref="AV39:AX39"/>
+    <mergeCell ref="E58:I58"/>
     <mergeCell ref="BE20:BG20"/>
     <mergeCell ref="AJ38:AL38"/>
     <mergeCell ref="BE35:BG35"/>
@@ -13871,6 +15474,7 @@
     <mergeCell ref="E20:I20"/>
     <mergeCell ref="J39:P39"/>
     <mergeCell ref="AG37:AI37"/>
+    <mergeCell ref="AE62:AF62"/>
     <mergeCell ref="AG47:AI47"/>
     <mergeCell ref="AF8:AH8"/>
     <mergeCell ref="BB27:BD27"/>
@@ -13880,28 +15484,38 @@
     <mergeCell ref="AM55:AO55"/>
     <mergeCell ref="X23:AD23"/>
     <mergeCell ref="BE38:BG38"/>
+    <mergeCell ref="AE64:AF64"/>
+    <mergeCell ref="AS62:AU62"/>
+    <mergeCell ref="AV63:AX63"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="AP53:AR53"/>
     <mergeCell ref="X16:AD16"/>
     <mergeCell ref="AP28:AR28"/>
     <mergeCell ref="BK53:BQ53"/>
+    <mergeCell ref="BH60:BJ60"/>
     <mergeCell ref="AC7:AE7"/>
     <mergeCell ref="AY26:BA26"/>
     <mergeCell ref="BE15:BG15"/>
+    <mergeCell ref="AS64:AU64"/>
+    <mergeCell ref="AG63:AI63"/>
     <mergeCell ref="X18:AD18"/>
     <mergeCell ref="BE33:BG33"/>
     <mergeCell ref="BB37:BD37"/>
     <mergeCell ref="AG50:AI50"/>
     <mergeCell ref="BK13:BQ13"/>
+    <mergeCell ref="AM58:AO58"/>
     <mergeCell ref="BE41:BG41"/>
+    <mergeCell ref="Q59:W59"/>
     <mergeCell ref="J25:P25"/>
     <mergeCell ref="Q46:W46"/>
     <mergeCell ref="BH55:BJ55"/>
     <mergeCell ref="AM24:AO24"/>
     <mergeCell ref="AG27:AI27"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="AM60:AO60"/>
     <mergeCell ref="BB38:BD38"/>
     <mergeCell ref="AV14:AX14"/>
+    <mergeCell ref="Q61:W61"/>
     <mergeCell ref="W3:AH3"/>
     <mergeCell ref="E33:I33"/>
     <mergeCell ref="Q48:W48"/>
@@ -13957,6 +15571,7 @@
     <mergeCell ref="Q36:W36"/>
     <mergeCell ref="BE54:BG54"/>
     <mergeCell ref="Q30:W30"/>
+    <mergeCell ref="AE63:AF63"/>
     <mergeCell ref="X26:AD26"/>
     <mergeCell ref="W1:AH1"/>
     <mergeCell ref="AC8:AE8"/>
@@ -13965,11 +15580,17 @@
     <mergeCell ref="BE56:BG56"/>
     <mergeCell ref="BE43:BG43"/>
     <mergeCell ref="J33:P33"/>
+    <mergeCell ref="AE58:AF58"/>
+    <mergeCell ref="BB59:BD59"/>
+    <mergeCell ref="AM63:AO63"/>
     <mergeCell ref="X27:AD27"/>
     <mergeCell ref="BB46:BD46"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="AY60:BA60"/>
+    <mergeCell ref="BB61:BD61"/>
     <mergeCell ref="AV15:AX15"/>
     <mergeCell ref="AY16:BA16"/>
+    <mergeCell ref="Q62:W62"/>
     <mergeCell ref="BB48:BD48"/>
     <mergeCell ref="AG43:AI43"/>
     <mergeCell ref="B32:D32"/>
@@ -13978,6 +15599,7 @@
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="AY45:BA45"/>
     <mergeCell ref="E36:I36"/>
+    <mergeCell ref="Q64:W64"/>
     <mergeCell ref="Q51:W51"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="BH45:BJ45"/>
@@ -14000,6 +15622,7 @@
     <mergeCell ref="BE50:BG50"/>
     <mergeCell ref="BE44:BG44"/>
     <mergeCell ref="AP19:AR19"/>
+    <mergeCell ref="AG61:AI61"/>
     <mergeCell ref="BE31:BG31"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="AG48:AI48"/>
@@ -14007,9 +15630,11 @@
     <mergeCell ref="B44:D44"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="J23:P23"/>
+    <mergeCell ref="BH58:BJ58"/>
     <mergeCell ref="AV28:AX28"/>
     <mergeCell ref="BK44:BQ44"/>
     <mergeCell ref="AY48:BA48"/>
+    <mergeCell ref="AG62:AI62"/>
     <mergeCell ref="AE33:AF33"/>
     <mergeCell ref="BB36:BD36"/>
     <mergeCell ref="X40:AD40"/>
@@ -14028,6 +15653,7 @@
     <mergeCell ref="AY37:BA37"/>
     <mergeCell ref="AS35:AU35"/>
     <mergeCell ref="J36:P36"/>
+    <mergeCell ref="BB62:BD62"/>
     <mergeCell ref="AJ14:AL14"/>
     <mergeCell ref="AY17:BA17"/>
     <mergeCell ref="AY53:BA53"/>
@@ -14036,17 +15662,21 @@
     <mergeCell ref="E50:I50"/>
     <mergeCell ref="AG11:AI11"/>
     <mergeCell ref="BH53:BJ53"/>
+    <mergeCell ref="BB64:BD64"/>
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="AV23:AX23"/>
     <mergeCell ref="BB51:BD51"/>
+    <mergeCell ref="AP63:AR63"/>
     <mergeCell ref="E42:I42"/>
     <mergeCell ref="AY55:BA55"/>
+    <mergeCell ref="X59:AD59"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="E44:I44"/>
     <mergeCell ref="BK19:BQ19"/>
     <mergeCell ref="X46:AD46"/>
     <mergeCell ref="BH48:BJ48"/>
     <mergeCell ref="AV24:AX24"/>
+    <mergeCell ref="BE58:BG58"/>
     <mergeCell ref="T8:V8"/>
     <mergeCell ref="AP27:AR27"/>
     <mergeCell ref="AS28:AU28"/>
@@ -14061,7 +15691,9 @@
     <mergeCell ref="AJ25:AL25"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="BE53:BG53"/>
+    <mergeCell ref="AJ60:AL60"/>
     <mergeCell ref="AM32:AO32"/>
+    <mergeCell ref="AG64:AI64"/>
     <mergeCell ref="Q7:S7"/>
     <mergeCell ref="AM26:AO26"/>
     <mergeCell ref="J24:P24"/>
@@ -14069,8 +15701,10 @@
     <mergeCell ref="Q20:W20"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="Q14:W14"/>
+    <mergeCell ref="B59:D59"/>
     <mergeCell ref="AV50:AX50"/>
     <mergeCell ref="B46:D46"/>
+    <mergeCell ref="Q60:W60"/>
     <mergeCell ref="AS54:AU54"/>
     <mergeCell ref="E32:I32"/>
     <mergeCell ref="J26:P26"/>
@@ -14087,18 +15721,21 @@
     <mergeCell ref="AP38:AR38"/>
     <mergeCell ref="X41:AD41"/>
     <mergeCell ref="AS43:AU43"/>
+    <mergeCell ref="AY63:BA63"/>
     <mergeCell ref="BE25:BG25"/>
     <mergeCell ref="BK38:BQ38"/>
     <mergeCell ref="F4:AH4"/>
     <mergeCell ref="X51:AD51"/>
     <mergeCell ref="AJ13:AL13"/>
     <mergeCell ref="AM52:AO52"/>
+    <mergeCell ref="BH61:BJ61"/>
     <mergeCell ref="AG17:AI17"/>
     <mergeCell ref="AS36:AU36"/>
     <mergeCell ref="J50:P50"/>
     <mergeCell ref="AM39:AO39"/>
     <mergeCell ref="AP40:AR40"/>
     <mergeCell ref="J42:P42"/>
+    <mergeCell ref="BK63:BQ63"/>
     <mergeCell ref="AJ15:AL15"/>
     <mergeCell ref="Q13:W13"/>
     <mergeCell ref="AG19:AI19"/>
@@ -14107,8 +15744,11 @@
     <mergeCell ref="J44:P44"/>
     <mergeCell ref="Q25:W25"/>
     <mergeCell ref="AV37:AX37"/>
+    <mergeCell ref="E60:I60"/>
     <mergeCell ref="J37:P37"/>
+    <mergeCell ref="AV60:AX60"/>
     <mergeCell ref="Q33:W33"/>
+    <mergeCell ref="X61:AD61"/>
     <mergeCell ref="BK27:BQ27"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="AV45:AX45"/>
@@ -14119,6 +15759,7 @@
     <mergeCell ref="AV26:AX26"/>
     <mergeCell ref="E45:I45"/>
     <mergeCell ref="AM42:AO42"/>
+    <mergeCell ref="X62:AD62"/>
     <mergeCell ref="AE37:AF37"/>
     <mergeCell ref="BH16:BJ16"/>
     <mergeCell ref="BB19:BD19"/>
@@ -14128,32 +15769,43 @@
     <mergeCell ref="AV27:AX27"/>
     <mergeCell ref="BE55:BG55"/>
     <mergeCell ref="AS31:AU31"/>
+    <mergeCell ref="X64:AD64"/>
     <mergeCell ref="BH18:BJ18"/>
     <mergeCell ref="J32:P32"/>
+    <mergeCell ref="J63:P63"/>
     <mergeCell ref="AE26:AF26"/>
     <mergeCell ref="AY38:BA38"/>
     <mergeCell ref="Q22:W22"/>
+    <mergeCell ref="BB58:BD58"/>
+    <mergeCell ref="B61:D61"/>
     <mergeCell ref="J47:P47"/>
+    <mergeCell ref="AV58:AX58"/>
     <mergeCell ref="BB20:BD20"/>
     <mergeCell ref="BB14:BD14"/>
     <mergeCell ref="AY24:BA24"/>
     <mergeCell ref="AJ28:AL28"/>
     <mergeCell ref="BK17:BQ17"/>
     <mergeCell ref="BK55:BQ55"/>
+    <mergeCell ref="BB60:BD60"/>
     <mergeCell ref="AP30:AR30"/>
+    <mergeCell ref="AP59:AR59"/>
     <mergeCell ref="AJ30:AL30"/>
     <mergeCell ref="AP46:AR46"/>
+    <mergeCell ref="BK59:BQ59"/>
     <mergeCell ref="BK46:BQ46"/>
     <mergeCell ref="BK40:BQ40"/>
     <mergeCell ref="AE42:AF42"/>
     <mergeCell ref="AY19:BA19"/>
     <mergeCell ref="BK25:BQ25"/>
+    <mergeCell ref="AP61:AR61"/>
     <mergeCell ref="AM16:AO16"/>
     <mergeCell ref="AP48:AR48"/>
+    <mergeCell ref="B64:D64"/>
     <mergeCell ref="AE44:AF44"/>
     <mergeCell ref="K6:M6"/>
     <mergeCell ref="AP41:AR41"/>
     <mergeCell ref="AM18:AO18"/>
+    <mergeCell ref="J60:P60"/>
     <mergeCell ref="BK41:BQ41"/>
     <mergeCell ref="BB13:BD13"/>
     <mergeCell ref="AM17:AO17"/>
@@ -14187,7 +15839,9 @@
     <mergeCell ref="BH17:BJ17"/>
     <mergeCell ref="E48:I48"/>
     <mergeCell ref="AE47:AF47"/>
+    <mergeCell ref="AY59:BA59"/>
     <mergeCell ref="Q6:S6"/>
+    <mergeCell ref="J58:P58"/>
     <mergeCell ref="AS32:AU32"/>
     <mergeCell ref="AM45:AO45"/>
     <mergeCell ref="AP11:AR11"/>
@@ -14201,31 +15855,47 @@
     <mergeCell ref="AY54:BA54"/>
     <mergeCell ref="AG33:AI33"/>
     <mergeCell ref="X17:AD17"/>
+    <mergeCell ref="BK61:BQ61"/>
     <mergeCell ref="AJ44:AL44"/>
     <mergeCell ref="Q54:W54"/>
     <mergeCell ref="BE18:BG18"/>
     <mergeCell ref="AY27:BA27"/>
     <mergeCell ref="AJ31:AL31"/>
     <mergeCell ref="AG35:AI35"/>
+    <mergeCell ref="B62:D62"/>
     <mergeCell ref="AM51:AO51"/>
     <mergeCell ref="Q23:W23"/>
     <mergeCell ref="X19:AD19"/>
+    <mergeCell ref="AE60:AF60"/>
+    <mergeCell ref="AS58:AU58"/>
+    <mergeCell ref="AV59:AX59"/>
+    <mergeCell ref="AP62:AR62"/>
     <mergeCell ref="E16:I16"/>
     <mergeCell ref="AV46:AX46"/>
     <mergeCell ref="Q31:W31"/>
     <mergeCell ref="AS50:AU50"/>
+    <mergeCell ref="BK62:BQ62"/>
     <mergeCell ref="E10:I11"/>
     <mergeCell ref="BK56:BQ56"/>
     <mergeCell ref="BE36:BG36"/>
     <mergeCell ref="BH37:BJ37"/>
     <mergeCell ref="AE45:AF45"/>
+    <mergeCell ref="X58:AD58"/>
+    <mergeCell ref="AS60:AU60"/>
+    <mergeCell ref="AV61:AX61"/>
+    <mergeCell ref="AP64:AR64"/>
     <mergeCell ref="Z7:AB7"/>
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="AP51:AR51"/>
+    <mergeCell ref="AG59:AI59"/>
+    <mergeCell ref="BK64:BQ64"/>
     <mergeCell ref="BK51:BQ51"/>
+    <mergeCell ref="X60:AD60"/>
+    <mergeCell ref="AM61:AO61"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="BB54:BD54"/>
+    <mergeCell ref="AE59:AF59"/>
     <mergeCell ref="AE22:AF22"/>
     <mergeCell ref="BB41:BD41"/>
     <mergeCell ref="J46:P46"/>
@@ -14236,6 +15906,7 @@
     <mergeCell ref="AM20:AO20"/>
     <mergeCell ref="AJ24:AL24"/>
     <mergeCell ref="B19:D19"/>
+    <mergeCell ref="J61:P61"/>
     <mergeCell ref="AY11:BA11"/>
     <mergeCell ref="J48:P48"/>
     <mergeCell ref="AM35:AO35"/>
@@ -14300,15 +15971,21 @@
     <mergeCell ref="E19:I19"/>
     <mergeCell ref="BE52:BG52"/>
     <mergeCell ref="BB56:BD56"/>
+    <mergeCell ref="AE61:AF61"/>
+    <mergeCell ref="AV64:AX64"/>
     <mergeCell ref="AF7:AH7"/>
     <mergeCell ref="BH15:BJ15"/>
     <mergeCell ref="AY30:BA30"/>
     <mergeCell ref="AJ32:AL32"/>
+    <mergeCell ref="AJ63:AL63"/>
     <mergeCell ref="AP25:AR25"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="AY46:BA46"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="Q58:W58"/>
+    <mergeCell ref="AY61:BA61"/>
     <mergeCell ref="AV16:AX16"/>
+    <mergeCell ref="Q63:W63"/>
     <mergeCell ref="AJ40:AL40"/>
     <mergeCell ref="Q50:W50"/>
     <mergeCell ref="AJ27:AL27"/>
@@ -14321,10 +15998,12 @@
     <mergeCell ref="X33:AD33"/>
     <mergeCell ref="AV17:AX17"/>
     <mergeCell ref="AY56:BA56"/>
+    <mergeCell ref="AM59:AO59"/>
     <mergeCell ref="AV11:AX11"/>
     <mergeCell ref="AP20:AR20"/>
     <mergeCell ref="AY43:BA43"/>
     <mergeCell ref="BE32:BG32"/>
+    <mergeCell ref="BE63:BG63"/>
     <mergeCell ref="BK14:BQ14"/>
     <mergeCell ref="AE16:AF16"/>
     <mergeCell ref="AG32:AI32"/>
@@ -14333,6 +16012,7 @@
     <mergeCell ref="BH43:BJ43"/>
     <mergeCell ref="BE47:BG47"/>
     <mergeCell ref="AP22:AR22"/>
+    <mergeCell ref="BK60:BQ60"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="J18:P18"/>
     <mergeCell ref="AE18:AF18"/>
@@ -14348,13 +16028,16 @@
     <mergeCell ref="AV44:AX44"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="AJ45:AL45"/>
+    <mergeCell ref="E63:I63"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="BB52:BD52"/>
     <mergeCell ref="AJ55:AL55"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="J19:P19"/>
+    <mergeCell ref="BH59:BJ59"/>
     <mergeCell ref="AY25:BA25"/>
     <mergeCell ref="BB45:BD45"/>
+    <mergeCell ref="AG58:AI58"/>
     <mergeCell ref="BB32:BD32"/>
     <mergeCell ref="Q55:W55"/>
     <mergeCell ref="AY36:BA36"/>
@@ -14362,6 +16045,7 @@
     <mergeCell ref="X28:AD28"/>
     <mergeCell ref="AS30:AU30"/>
     <mergeCell ref="BB47:BD47"/>
+    <mergeCell ref="AG60:AI60"/>
     <mergeCell ref="N7:P7"/>
     <mergeCell ref="AS42:AU42"/>
     <mergeCell ref="BH54:BJ54"/>
@@ -14369,6 +16053,7 @@
     <mergeCell ref="BH41:BJ41"/>
     <mergeCell ref="X30:AD30"/>
     <mergeCell ref="BE45:BG45"/>
+    <mergeCell ref="AJ58:AL58"/>
     <mergeCell ref="X42:AD42"/>
     <mergeCell ref="E22:I22"/>
     <mergeCell ref="BH56:BJ56"/>
@@ -14376,12 +16061,16 @@
     <mergeCell ref="BH31:BJ31"/>
     <mergeCell ref="AJ48:AL48"/>
     <mergeCell ref="AV42:AX42"/>
+    <mergeCell ref="BE59:BG59"/>
+    <mergeCell ref="AY62:BA62"/>
+    <mergeCell ref="BB63:BD63"/>
     <mergeCell ref="BE46:BG46"/>
     <mergeCell ref="BB50:BD50"/>
     <mergeCell ref="X54:AD54"/>
     <mergeCell ref="BK20:BQ20"/>
     <mergeCell ref="AY28:BA28"/>
     <mergeCell ref="B28:D28"/>
+    <mergeCell ref="AY64:BA64"/>
     <mergeCell ref="AV19:AX19"/>
     <mergeCell ref="AS23:AU23"/>
     <mergeCell ref="E38:I38"/>
@@ -14400,12 +16089,14 @@
     <mergeCell ref="AV20:AX20"/>
     <mergeCell ref="BE48:BG48"/>
     <mergeCell ref="AS24:AU24"/>
+    <mergeCell ref="A57:BQ57"/>
     <mergeCell ref="AS18:AU18"/>
     <mergeCell ref="AM27:AO27"/>
     <mergeCell ref="BH36:BJ36"/>
     <mergeCell ref="BH11:BJ11"/>
     <mergeCell ref="AE19:AF19"/>
     <mergeCell ref="Z6:AB6"/>
+    <mergeCell ref="AJ59:AL59"/>
     <mergeCell ref="B54:D54"/>
     <mergeCell ref="AS26:AU26"/>
     <mergeCell ref="AJ46:AL46"/>
@@ -14418,6 +16109,7 @@
     <mergeCell ref="AP23:AR23"/>
     <mergeCell ref="B56:D56"/>
     <mergeCell ref="J20:P20"/>
+    <mergeCell ref="AJ61:AL61"/>
     <mergeCell ref="AV47:AX47"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="BE51:BG51"/>
@@ -14427,6 +16119,7 @@
     <mergeCell ref="A34:BQ34"/>
     <mergeCell ref="A5:S5"/>
     <mergeCell ref="J22:P22"/>
+    <mergeCell ref="BH62:BJ62"/>
     <mergeCell ref="AV38:AX38"/>
     <mergeCell ref="A49:BQ49"/>
     <mergeCell ref="AY52:BA52"/>
@@ -14443,6 +16136,7 @@
     <mergeCell ref="E28:I28"/>
     <mergeCell ref="AG13:AI13"/>
     <mergeCell ref="AV33:AX33"/>
+    <mergeCell ref="BE61:BG61"/>
     <mergeCell ref="AP36:AR36"/>
     <mergeCell ref="AS37:AU37"/>
     <mergeCell ref="AE14:AF14"/>
@@ -14456,18 +16150,23 @@
     <mergeCell ref="AJ16:AL16"/>
     <mergeCell ref="X32:AD32"/>
     <mergeCell ref="B36:D36"/>
+    <mergeCell ref="E59:I59"/>
     <mergeCell ref="E46:I46"/>
     <mergeCell ref="J40:P40"/>
+    <mergeCell ref="BE62:BG62"/>
     <mergeCell ref="J15:P15"/>
     <mergeCell ref="AM41:AO41"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="E61:I61"/>
     <mergeCell ref="A29:BQ29"/>
     <mergeCell ref="AV35:AX35"/>
     <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="E54:I54"/>
+    <mergeCell ref="BE64:BG64"/>
     <mergeCell ref="AV22:AX22"/>
     <mergeCell ref="AY23:BA23"/>
+    <mergeCell ref="AS63:AU63"/>
     <mergeCell ref="E41:I41"/>
     <mergeCell ref="J35:P35"/>
     <mergeCell ref="AE27:AF27"/>
@@ -14477,6 +16176,7 @@
     <mergeCell ref="E56:I56"/>
     <mergeCell ref="AV51:AX51"/>
     <mergeCell ref="E43:I43"/>
+    <mergeCell ref="X63:AD63"/>
     <mergeCell ref="BB15:BD15"/>
     <mergeCell ref="BE16:BG16"/>
     <mergeCell ref="AE20:AF20"/>
@@ -14490,18 +16190,21 @@
     <mergeCell ref="AE35:AF35"/>
     <mergeCell ref="BH14:BJ14"/>
     <mergeCell ref="BK54:BQ54"/>
+    <mergeCell ref="AJ62:AL62"/>
     <mergeCell ref="AJ37:AL37"/>
     <mergeCell ref="BE11:BG11"/>
     <mergeCell ref="AY20:BA20"/>
     <mergeCell ref="AG28:AI28"/>
     <mergeCell ref="Q16:W16"/>
     <mergeCell ref="AV40:AX40"/>
+    <mergeCell ref="AJ64:AL64"/>
     <mergeCell ref="T7:V7"/>
     <mergeCell ref="J28:P28"/>
     <mergeCell ref="X52:AD52"/>
     <mergeCell ref="Q24:W24"/>
     <mergeCell ref="AG30:AI30"/>
     <mergeCell ref="Q18:W18"/>
+    <mergeCell ref="B63:D63"/>
     <mergeCell ref="AM37:AO37"/>
     <mergeCell ref="AE38:AF38"/>
     <mergeCell ref="AV54:AX54"/>
@@ -14518,23 +16221,29 @@
     <mergeCell ref="AM14:AO14"/>
     <mergeCell ref="AE15:AF15"/>
     <mergeCell ref="AP42:AR42"/>
+    <mergeCell ref="BH63:BJ63"/>
     <mergeCell ref="AJ42:AL42"/>
+    <mergeCell ref="AP58:AR58"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="AM13:AO13"/>
     <mergeCell ref="AP52:AR52"/>
     <mergeCell ref="X55:AD55"/>
     <mergeCell ref="AJ17:AL17"/>
     <mergeCell ref="AM56:AO56"/>
+    <mergeCell ref="AM62:AO62"/>
     <mergeCell ref="J54:P54"/>
     <mergeCell ref="AM43:AO43"/>
     <mergeCell ref="J41:P41"/>
     <mergeCell ref="Q44:W44"/>
     <mergeCell ref="AV43:AX43"/>
     <mergeCell ref="AJ19:AL19"/>
+    <mergeCell ref="E62:I62"/>
     <mergeCell ref="J56:P56"/>
+    <mergeCell ref="AY58:BA58"/>
     <mergeCell ref="J43:P43"/>
     <mergeCell ref="X25:AD25"/>
     <mergeCell ref="AG16:AI16"/>
+    <mergeCell ref="E64:I64"/>
     <mergeCell ref="E51:I51"/>
     <mergeCell ref="BK31:BQ31"/>
     <mergeCell ref="AG18:AI18"/>
@@ -14542,8 +16251,10 @@
     <mergeCell ref="B55:D55"/>
     <mergeCell ref="AM25:AO25"/>
     <mergeCell ref="N6:P6"/>
+    <mergeCell ref="J59:P59"/>
     <mergeCell ref="AP32:AR32"/>
     <mergeCell ref="BK45:BQ45"/>
+    <mergeCell ref="BH64:BJ64"/>
     <mergeCell ref="BE19:BG19"/>
     <mergeCell ref="BK32:BQ32"/>
     <mergeCell ref="AM33:AO33"/>
@@ -14558,6 +16269,7 @@
     <mergeCell ref="Q26:W26"/>
     <mergeCell ref="AG10:AU10"/>
     <mergeCell ref="AG44:AI44"/>
+    <mergeCell ref="AV62:AX62"/>
     <mergeCell ref="BE14:BG14"/>
     <mergeCell ref="BB24:BD24"/>
     <mergeCell ref="AM28:AO28"/>
@@ -14565,15 +16277,17 @@
     <mergeCell ref="AG31:AI31"/>
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="AV56:AX56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="BE60:BG60"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE20 AE22:AE28 AE30:AE33 AE35:AE48 AE50:AE56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE20 AE22:AE28 AE30:AE33 AE35:AE48 AE50:AE56 AE58:AE64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG20 AG22:AG28 AG30:AG33 AG35:AG48 AG50:AG56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG20 AG22:AG28 AG30:AG33 AG35:AG48 AG50:AG56 AG58:AG64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV20 AV22:AV28 AV30:AV33 AV35:AV48 AV50:AV56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV20 AV22:AV28 AV30:AV33 AV35:AV48 AV50:AV56 AV58:AV64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
